--- a/Assets/Resources/DataBase/Upgrade Data/UpgradeDB.xlsx
+++ b/Assets/Resources/DataBase/Upgrade Data/UpgradeDB.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\LastDance\Assets\Resources\DataBase\Upgrade Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D400963-C749-46FF-AABF-D2B6012D9441}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CC71718-D5C7-44F4-94A9-5D6AD98F2E2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" xr2:uid="{0FBE682E-FB0C-4418-8BE2-F8F6B88AE61D}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <si>
     <t>index</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -112,6 +112,26 @@
   </si>
   <si>
     <t>value</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>주유구 추가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>주유 속도 증가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>돈 배율</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>빠른 폐차 수수료</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>폐차 보너스</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -496,12 +516,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C4FEBA7-623E-4EAA-9C7F-E935E0D89B65}">
-  <dimension ref="A1:V1"/>
+  <dimension ref="A1:V6"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="6.83203125" customWidth="1"/>
     <col min="2" max="2" width="12.58203125" customWidth="1"/>
-    <col min="3" max="3" width="13.5" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.45">
@@ -570,6 +590,46 @@
       </c>
       <c r="V1" t="s">
         <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="C4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="C5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="C6" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resources/DataBase/Upgrade Data/UpgradeDB.xlsx
+++ b/Assets/Resources/DataBase/Upgrade Data/UpgradeDB.xlsx
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>index</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -127,6 +127,14 @@
   </si>
   <si>
     <t>안녕하세용</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>테스트12312</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Percent</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -511,7 +519,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:V3"/>
+  <dimension ref="A1:V4"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6.796875" customWidth="1"/>
@@ -723,6 +731,74 @@
         <v>9</v>
       </c>
     </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.4">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4">
+        <v>5</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+      <c r="N4">
+        <v>1</v>
+      </c>
+      <c r="O4">
+        <v>1</v>
+      </c>
+      <c r="P4">
+        <v>1</v>
+      </c>
+      <c r="Q4">
+        <v>1</v>
+      </c>
+      <c r="R4">
+        <v>1</v>
+      </c>
+      <c r="S4">
+        <v>1</v>
+      </c>
+      <c r="T4">
+        <v>1</v>
+      </c>
+      <c r="U4">
+        <v>1</v>
+      </c>
+      <c r="V4">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Assets/Resources/DataBase/Upgrade Data/UpgradeDB.xlsx
+++ b/Assets/Resources/DataBase/Upgrade Data/UpgradeDB.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\LastDance\Assets\Resources\DataBase\Upgrade Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CC71718-D5C7-44F4-94A9-5D6AD98F2E2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{896F1113-4ABD-4E97-89BA-65466E5AD204}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" xr2:uid="{0FBE682E-FB0C-4418-8BE2-F8F6B88AE61D}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="31">
   <si>
     <t>index</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -123,15 +123,31 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>돈 배율</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>빠른 폐차 수수료</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>폐차 보너스</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>percent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>add</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Multiply</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>주유 보너스</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lv0value</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -139,6 +155,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="178" formatCode="0_);[Red]\(0\)"/>
+  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -178,8 +197,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -516,15 +541,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C4FEBA7-623E-4EAA-9C7F-E935E0D89B65}">
-  <dimension ref="A1:V6"/>
+  <dimension ref="A1:W6"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="6.83203125" customWidth="1"/>
     <col min="2" max="2" width="12.58203125" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="22" max="22" width="9.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -538,98 +564,339 @@
         <v>1</v>
       </c>
       <c r="E1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1" t="s">
         <v>2</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>11</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>4</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>12</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>5</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>13</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>6</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>14</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>7</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>15</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>8</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>16</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>9</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>10</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>18</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>19</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A2">
         <v>1</v>
       </c>
+      <c r="B2" t="s">
+        <v>26</v>
+      </c>
       <c r="C2" t="s">
-        <v>22</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="D2">
+        <v>8</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>100</v>
+      </c>
+      <c r="G2" s="2">
+        <v>15</v>
+      </c>
+      <c r="H2">
+        <v>1000</v>
+      </c>
+      <c r="I2" s="2">
+        <v>30</v>
+      </c>
+      <c r="J2" s="2">
+        <v>5000</v>
+      </c>
+      <c r="K2" s="2">
+        <v>40</v>
+      </c>
+      <c r="L2" s="2">
+        <v>10000</v>
+      </c>
+      <c r="M2" s="2">
+        <v>50</v>
+      </c>
+      <c r="N2" s="2">
+        <v>50000</v>
+      </c>
+      <c r="O2" s="2">
+        <v>60</v>
+      </c>
+      <c r="P2" s="2">
+        <v>100000</v>
+      </c>
+      <c r="Q2" s="2">
+        <v>70</v>
+      </c>
+      <c r="R2" s="2">
+        <v>300000</v>
+      </c>
+      <c r="S2" s="2">
+        <v>75</v>
+      </c>
+      <c r="T2" s="2">
+        <v>500000</v>
+      </c>
+      <c r="U2" s="2">
+        <v>80</v>
+      </c>
+      <c r="V2" s="2">
+        <v>1000000</v>
+      </c>
+      <c r="W2" s="1"/>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A3">
         <v>2</v>
       </c>
+      <c r="B3" t="s">
+        <v>26</v>
+      </c>
       <c r="C3" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="D3">
+        <v>8</v>
+      </c>
+      <c r="E3">
+        <v>100</v>
+      </c>
+      <c r="F3">
+        <v>1000</v>
+      </c>
+      <c r="G3">
+        <v>90</v>
+      </c>
+      <c r="H3" s="2">
+        <v>7000</v>
+      </c>
+      <c r="I3">
+        <v>80</v>
+      </c>
+      <c r="J3" s="2">
+        <v>50000</v>
+      </c>
+      <c r="K3">
+        <v>70</v>
+      </c>
+      <c r="L3" s="2">
+        <v>150000</v>
+      </c>
+      <c r="M3">
+        <v>60</v>
+      </c>
+      <c r="N3" s="2">
+        <v>500000</v>
+      </c>
+      <c r="O3">
+        <v>50</v>
+      </c>
+      <c r="P3" s="2">
+        <v>1000000</v>
+      </c>
+      <c r="Q3">
+        <v>40</v>
+      </c>
+      <c r="R3" s="2">
+        <v>2000000</v>
+      </c>
+      <c r="S3">
+        <v>35</v>
+      </c>
+      <c r="T3" s="2">
+        <v>500000</v>
+      </c>
+      <c r="U3">
+        <v>30</v>
+      </c>
+      <c r="V3" s="2">
+        <v>10000000</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A4">
         <v>3</v>
       </c>
+      <c r="B4" t="s">
+        <v>28</v>
+      </c>
       <c r="C4" t="s">
-        <v>24</v>
+        <v>29</v>
+      </c>
+      <c r="D4">
+        <v>6</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>500</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+      <c r="H4">
+        <v>5000</v>
+      </c>
+      <c r="I4">
+        <v>3</v>
+      </c>
+      <c r="J4">
+        <v>30000</v>
+      </c>
+      <c r="K4">
+        <v>3.5</v>
+      </c>
+      <c r="L4">
+        <v>100000</v>
+      </c>
+      <c r="M4">
+        <v>4</v>
+      </c>
+      <c r="N4">
+        <v>300000</v>
+      </c>
+      <c r="O4">
+        <v>4.5</v>
+      </c>
+      <c r="P4">
+        <v>500000</v>
+      </c>
+      <c r="Q4">
+        <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A5">
         <v>4</v>
       </c>
+      <c r="B5" t="s">
+        <v>28</v>
+      </c>
       <c r="C5" t="s">
         <v>25</v>
       </c>
+      <c r="D5">
+        <v>6</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>500</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+      <c r="H5">
+        <v>5000</v>
+      </c>
+      <c r="I5">
+        <v>3</v>
+      </c>
+      <c r="J5">
+        <v>30000</v>
+      </c>
+      <c r="K5">
+        <v>3.5</v>
+      </c>
+      <c r="L5">
+        <v>100000</v>
+      </c>
+      <c r="M5">
+        <v>4</v>
+      </c>
+      <c r="N5">
+        <v>300000</v>
+      </c>
+      <c r="O5">
+        <v>4.5</v>
+      </c>
+      <c r="P5">
+        <v>500000</v>
+      </c>
+      <c r="Q5">
+        <v>5</v>
+      </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A6">
         <v>5</v>
       </c>
+      <c r="B6" t="s">
+        <v>27</v>
+      </c>
       <c r="C6" t="s">
-        <v>26</v>
+        <v>22</v>
+      </c>
+      <c r="D6">
+        <v>4</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>10000</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+      <c r="H6">
+        <v>100000</v>
+      </c>
+      <c r="I6">
+        <v>3</v>
+      </c>
+      <c r="J6">
+        <v>1000000</v>
+      </c>
+      <c r="K6">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resources/DataBase/Upgrade Data/UpgradeDB.xlsx
+++ b/Assets/Resources/DataBase/Upgrade Data/UpgradeDB.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr defaultThemeVersion="202300"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\LastDance\Assets\Resources\DataBase\Upgrade Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JoYK\Documents\GitHub\Engine GenP 3D\LastDance\Assets\Resources\DataBase\Upgrade Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{896F1113-4ABD-4E97-89BA-65466E5AD204}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" xr2:uid="{0FBE682E-FB0C-4418-8BE2-F8F6B88AE61D}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="25824" windowHeight="16224"/>
   </bookViews>
   <sheets>
     <sheet name="UpgradeSheet" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -131,14 +130,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>percent</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>add</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Multiply</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -148,15 +139,23 @@
   </si>
   <si>
     <t>lv0value</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Percent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Add</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="1">
-    <numFmt numFmtId="178" formatCode="0_);[Red]\(0\)"/>
+    <numFmt numFmtId="176" formatCode="0_);[Red]\(0\)"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -204,7 +203,7 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -540,17 +539,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C4FEBA7-623E-4EAA-9C7F-E935E0D89B65}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:W6"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="6.83203125" customWidth="1"/>
-    <col min="2" max="2" width="12.58203125" customWidth="1"/>
+    <col min="1" max="1" width="6.796875" customWidth="1"/>
+    <col min="2" max="2" width="12.59765625" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="22" max="22" width="9.75" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="9.69921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -564,7 +563,7 @@
         <v>1</v>
       </c>
       <c r="E1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F1" t="s">
         <v>2</v>
@@ -621,12 +620,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C2" t="s">
         <v>23</v>
@@ -690,12 +689,12 @@
       </c>
       <c r="W2" s="1"/>
     </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C3" t="s">
         <v>24</v>
@@ -758,15 +757,15 @@
         <v>10000000</v>
       </c>
     </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D4">
         <v>6</v>
@@ -811,12 +810,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C5" t="s">
         <v>25</v>
@@ -864,12 +863,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C6" t="s">
         <v>22</v>

--- a/Assets/Resources/DataBase/Upgrade Data/UpgradeDB.xlsx
+++ b/Assets/Resources/DataBase/Upgrade Data/UpgradeDB.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JoYK\Documents\GitHub\Engine GenP 3D\LastDance\Assets\Resources\DataBase\Upgrade Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\LastDance\Assets\Resources\DataBase\Upgrade Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7793AC90-C76E-4623-9AC6-A8FA040CE384}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="25824" windowHeight="16224"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UpgradeSheet" sheetId="1" r:id="rId1"/>
@@ -18,17 +19,6 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="2"/>
@@ -153,7 +143,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0_);[Red]\(0\)"/>
   </numFmts>
@@ -196,14 +186,17 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -539,17 +532,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:W6"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="6.796875" customWidth="1"/>
-    <col min="2" max="2" width="12.59765625" customWidth="1"/>
+    <col min="1" max="1" width="6.83203125" customWidth="1"/>
+    <col min="2" max="2" width="12.58203125" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="22" max="22" width="9.69921875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="9.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -620,7 +613,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A2">
         <v>1</v>
       </c>
@@ -636,60 +629,62 @@
       <c r="E2">
         <v>0</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="2">
+        <v>10800</v>
+      </c>
+      <c r="G2" s="1">
+        <v>25</v>
+      </c>
+      <c r="H2" s="2">
+        <v>15700</v>
+      </c>
+      <c r="I2" s="1">
+        <v>50</v>
+      </c>
+      <c r="J2" s="2">
+        <v>22700</v>
+      </c>
+      <c r="K2" s="1">
+        <v>75</v>
+      </c>
+      <c r="L2" s="2">
+        <v>32900</v>
+      </c>
+      <c r="M2" s="1">
         <v>100</v>
       </c>
-      <c r="G2" s="2">
-        <v>15</v>
-      </c>
-      <c r="H2">
-        <v>1000</v>
-      </c>
-      <c r="I2" s="2">
-        <v>30</v>
-      </c>
-      <c r="J2" s="2">
-        <v>5000</v>
-      </c>
-      <c r="K2" s="2">
-        <v>40</v>
-      </c>
-      <c r="L2" s="2">
-        <v>10000</v>
-      </c>
-      <c r="M2" s="2">
-        <v>50</v>
-      </c>
       <c r="N2" s="2">
-        <v>50000</v>
-      </c>
-      <c r="O2" s="2">
-        <v>60</v>
+        <v>47700</v>
+      </c>
+      <c r="O2" s="1">
+        <v>125</v>
       </c>
       <c r="P2" s="2">
-        <v>100000</v>
-      </c>
-      <c r="Q2" s="2">
-        <v>70</v>
+        <v>69200</v>
+      </c>
+      <c r="Q2" s="1">
+        <v>150</v>
       </c>
       <c r="R2" s="2">
-        <v>300000</v>
-      </c>
-      <c r="S2" s="2">
-        <v>75</v>
+        <v>100400</v>
+      </c>
+      <c r="S2" s="1">
+        <v>175</v>
       </c>
       <c r="T2" s="2">
-        <v>500000</v>
-      </c>
-      <c r="U2" s="2">
-        <v>80</v>
+        <v>145500</v>
+      </c>
+      <c r="U2" s="1">
+        <v>200</v>
       </c>
       <c r="V2" s="2">
-        <v>1000000</v>
-      </c>
-      <c r="W2" s="1"/>
+        <v>211000</v>
+      </c>
+      <c r="W2" s="3">
+        <v>225</v>
+      </c>
     </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A3">
         <v>2</v>
       </c>
@@ -705,59 +700,62 @@
       <c r="E3">
         <v>100</v>
       </c>
-      <c r="F3">
-        <v>1000</v>
+      <c r="F3" s="2">
+        <v>30300</v>
       </c>
       <c r="G3">
         <v>90</v>
       </c>
       <c r="H3" s="2">
-        <v>7000</v>
+        <v>43900</v>
       </c>
       <c r="I3">
         <v>80</v>
       </c>
       <c r="J3" s="2">
-        <v>50000</v>
+        <v>63700</v>
       </c>
       <c r="K3">
         <v>70</v>
       </c>
       <c r="L3" s="2">
-        <v>150000</v>
+        <v>92300</v>
       </c>
       <c r="M3">
         <v>60</v>
       </c>
       <c r="N3" s="2">
-        <v>500000</v>
+        <v>133800</v>
       </c>
       <c r="O3">
         <v>50</v>
       </c>
       <c r="P3" s="2">
-        <v>1000000</v>
+        <v>194100</v>
       </c>
       <c r="Q3">
+        <v>45</v>
+      </c>
+      <c r="R3" s="2">
+        <v>281400</v>
+      </c>
+      <c r="S3">
         <v>40</v>
       </c>
-      <c r="R3" s="2">
-        <v>2000000</v>
-      </c>
-      <c r="S3">
+      <c r="T3" s="2">
+        <v>408000</v>
+      </c>
+      <c r="U3">
         <v>35</v>
       </c>
-      <c r="T3" s="2">
-        <v>500000</v>
-      </c>
-      <c r="U3">
+      <c r="V3" s="1">
+        <v>612500</v>
+      </c>
+      <c r="W3">
         <v>30</v>
       </c>
-      <c r="V3" s="2">
-        <v>10000000</v>
-      </c>
     </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A4">
         <v>3</v>
       </c>
@@ -773,44 +771,62 @@
       <c r="E4">
         <v>1</v>
       </c>
-      <c r="F4">
-        <v>500</v>
+      <c r="F4" s="2">
+        <v>21600</v>
       </c>
       <c r="G4">
         <v>2</v>
       </c>
-      <c r="H4">
-        <v>5000</v>
+      <c r="H4" s="2">
+        <v>32400</v>
       </c>
       <c r="I4">
         <v>3</v>
       </c>
-      <c r="J4">
-        <v>30000</v>
+      <c r="J4" s="2">
+        <v>48600</v>
       </c>
       <c r="K4">
-        <v>3.5</v>
-      </c>
-      <c r="L4">
-        <v>100000</v>
+        <v>4</v>
+      </c>
+      <c r="L4" s="2">
+        <v>72900</v>
       </c>
       <c r="M4">
-        <v>4</v>
-      </c>
-      <c r="N4">
-        <v>300000</v>
+        <v>5</v>
+      </c>
+      <c r="N4" s="2">
+        <v>109400</v>
       </c>
       <c r="O4">
-        <v>4.5</v>
-      </c>
-      <c r="P4">
-        <v>500000</v>
+        <v>5.5</v>
+      </c>
+      <c r="P4" s="2">
+        <v>164000</v>
       </c>
       <c r="Q4">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R4" s="2">
+        <v>246000</v>
+      </c>
+      <c r="S4">
+        <v>6.5</v>
+      </c>
+      <c r="T4" s="2">
+        <v>369100</v>
+      </c>
+      <c r="U4">
+        <v>7</v>
+      </c>
+      <c r="V4" s="2">
+        <v>553600</v>
+      </c>
+      <c r="W4">
+        <v>7.5</v>
       </c>
     </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A5">
         <v>4</v>
       </c>
@@ -826,44 +842,62 @@
       <c r="E5">
         <v>1</v>
       </c>
-      <c r="F5">
-        <v>500</v>
+      <c r="F5" s="2">
+        <v>18000</v>
       </c>
       <c r="G5">
         <v>2</v>
       </c>
-      <c r="H5">
-        <v>5000</v>
+      <c r="H5" s="2">
+        <v>27000</v>
       </c>
       <c r="I5">
         <v>3</v>
       </c>
-      <c r="J5">
-        <v>30000</v>
+      <c r="J5" s="2">
+        <v>40500</v>
       </c>
       <c r="K5">
-        <v>3.5</v>
-      </c>
-      <c r="L5">
-        <v>100000</v>
+        <v>4</v>
+      </c>
+      <c r="L5" s="2">
+        <v>60800</v>
       </c>
       <c r="M5">
-        <v>4</v>
-      </c>
-      <c r="N5">
-        <v>300000</v>
+        <v>5</v>
+      </c>
+      <c r="N5" s="2">
+        <v>91100</v>
       </c>
       <c r="O5">
-        <v>4.5</v>
-      </c>
-      <c r="P5">
-        <v>500000</v>
+        <v>5.5</v>
+      </c>
+      <c r="P5" s="2">
+        <v>136700</v>
       </c>
       <c r="Q5">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R5" s="2">
+        <v>205000</v>
+      </c>
+      <c r="S5">
+        <v>6.5</v>
+      </c>
+      <c r="T5" s="2">
+        <v>307500</v>
+      </c>
+      <c r="U5">
+        <v>7</v>
+      </c>
+      <c r="V5" s="2">
+        <v>461300</v>
+      </c>
+      <c r="W5">
+        <v>7.5</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A6">
         <v>5</v>
       </c>
@@ -879,20 +913,20 @@
       <c r="E6">
         <v>1</v>
       </c>
-      <c r="F6">
-        <v>10000</v>
+      <c r="F6" s="2">
+        <v>36000</v>
       </c>
       <c r="G6">
         <v>2</v>
       </c>
-      <c r="H6">
-        <v>100000</v>
+      <c r="H6" s="2">
+        <v>108000</v>
       </c>
       <c r="I6">
         <v>3</v>
       </c>
-      <c r="J6">
-        <v>1000000</v>
+      <c r="J6" s="2">
+        <v>324000</v>
       </c>
       <c r="K6">
         <v>4</v>

--- a/Assets/Resources/DataBase/Upgrade Data/UpgradeDB.xlsx
+++ b/Assets/Resources/DataBase/Upgrade Data/UpgradeDB.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\LastDance\Assets\Resources\DataBase\Upgrade Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7793AC90-C76E-4623-9AC6-A8FA040CE384}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44F597CF-6B53-435E-89EF-B395194ED9B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -186,17 +186,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -536,399 +530,401 @@
   <dimension ref="A1:W6"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="6.83203125" customWidth="1"/>
-    <col min="2" max="2" width="12.58203125" customWidth="1"/>
-    <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="22" max="22" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.83203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="12.58203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="16" style="1" customWidth="1"/>
+    <col min="4" max="21" width="8.6640625" style="1"/>
+    <col min="22" max="22" width="9.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.45">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="P1" t="s">
+      <c r="P1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" t="s">
+      <c r="R1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="S1" t="s">
+      <c r="S1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="T1" t="s">
+      <c r="T1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="U1" t="s">
+      <c r="U1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="V1" t="s">
+      <c r="V1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="W1" t="s">
+      <c r="W1" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.45">
-      <c r="A2">
+      <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="1">
         <v>8</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="1">
         <v>0</v>
       </c>
-      <c r="F2" s="2">
+      <c r="F2" s="1">
         <v>10800</v>
       </c>
       <c r="G2" s="1">
         <v>25</v>
       </c>
-      <c r="H2" s="2">
+      <c r="H2" s="1">
         <v>15700</v>
       </c>
       <c r="I2" s="1">
         <v>50</v>
       </c>
-      <c r="J2" s="2">
+      <c r="J2" s="1">
         <v>22700</v>
       </c>
       <c r="K2" s="1">
         <v>75</v>
       </c>
-      <c r="L2" s="2">
+      <c r="L2" s="1">
         <v>32900</v>
       </c>
       <c r="M2" s="1">
         <v>100</v>
       </c>
-      <c r="N2" s="2">
+      <c r="N2" s="1">
         <v>47700</v>
       </c>
       <c r="O2" s="1">
         <v>125</v>
       </c>
-      <c r="P2" s="2">
+      <c r="P2" s="1">
         <v>69200</v>
       </c>
       <c r="Q2" s="1">
         <v>150</v>
       </c>
-      <c r="R2" s="2">
+      <c r="R2" s="1">
         <v>100400</v>
       </c>
       <c r="S2" s="1">
         <v>175</v>
       </c>
-      <c r="T2" s="2">
+      <c r="T2" s="1">
         <v>145500</v>
       </c>
       <c r="U2" s="1">
         <v>200</v>
       </c>
-      <c r="V2" s="2">
+      <c r="V2" s="1">
         <v>211000</v>
       </c>
-      <c r="W2" s="3">
+      <c r="W2" s="1">
         <v>225</v>
       </c>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.45">
-      <c r="A3">
+      <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="1">
         <v>8</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="1">
         <v>100</v>
       </c>
-      <c r="F3" s="2">
+      <c r="F3" s="1">
         <v>30300</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="1">
         <v>90</v>
       </c>
-      <c r="H3" s="2">
+      <c r="H3" s="1">
         <v>43900</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="1">
         <v>80</v>
       </c>
-      <c r="J3" s="2">
+      <c r="J3" s="1">
         <v>63700</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="1">
         <v>70</v>
       </c>
-      <c r="L3" s="2">
+      <c r="L3" s="1">
         <v>92300</v>
       </c>
-      <c r="M3">
+      <c r="M3" s="1">
         <v>60</v>
       </c>
-      <c r="N3" s="2">
+      <c r="N3" s="1">
         <v>133800</v>
       </c>
-      <c r="O3">
+      <c r="O3" s="1">
         <v>50</v>
       </c>
-      <c r="P3" s="2">
+      <c r="P3" s="1">
         <v>194100</v>
       </c>
-      <c r="Q3">
+      <c r="Q3" s="1">
         <v>45</v>
       </c>
-      <c r="R3" s="2">
+      <c r="R3" s="1">
         <v>281400</v>
       </c>
-      <c r="S3">
+      <c r="S3" s="1">
         <v>40</v>
       </c>
-      <c r="T3" s="2">
+      <c r="T3" s="1">
         <v>408000</v>
       </c>
-      <c r="U3">
+      <c r="U3" s="1">
         <v>35</v>
       </c>
       <c r="V3" s="1">
         <v>612500</v>
       </c>
-      <c r="W3">
+      <c r="W3" s="1">
         <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.45">
-      <c r="A4">
+      <c r="A4" s="1">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="1">
         <v>6</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="1">
         <v>1</v>
       </c>
-      <c r="F4" s="2">
+      <c r="F4" s="1">
         <v>21600</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="1">
         <v>2</v>
       </c>
-      <c r="H4" s="2">
+      <c r="H4" s="1">
         <v>32400</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="1">
         <v>3</v>
       </c>
-      <c r="J4" s="2">
+      <c r="J4" s="1">
         <v>48600</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="1">
         <v>4</v>
       </c>
-      <c r="L4" s="2">
+      <c r="L4" s="1">
         <v>72900</v>
       </c>
-      <c r="M4">
+      <c r="M4" s="1">
         <v>5</v>
       </c>
-      <c r="N4" s="2">
+      <c r="N4" s="1">
         <v>109400</v>
       </c>
-      <c r="O4">
+      <c r="O4" s="1">
         <v>5.5</v>
       </c>
-      <c r="P4" s="2">
+      <c r="P4" s="1">
         <v>164000</v>
       </c>
-      <c r="Q4">
+      <c r="Q4" s="1">
         <v>6</v>
       </c>
-      <c r="R4" s="2">
+      <c r="R4" s="1">
         <v>246000</v>
       </c>
-      <c r="S4">
+      <c r="S4" s="1">
         <v>6.5</v>
       </c>
-      <c r="T4" s="2">
+      <c r="T4" s="1">
         <v>369100</v>
       </c>
-      <c r="U4">
+      <c r="U4" s="1">
         <v>7</v>
       </c>
-      <c r="V4" s="2">
+      <c r="V4" s="1">
         <v>553600</v>
       </c>
-      <c r="W4">
+      <c r="W4" s="1">
         <v>7.5</v>
       </c>
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.45">
-      <c r="A5">
+      <c r="A5" s="1">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="1">
         <v>6</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="1">
         <v>1</v>
       </c>
-      <c r="F5" s="2">
+      <c r="F5" s="1">
         <v>18000</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="1">
         <v>2</v>
       </c>
-      <c r="H5" s="2">
+      <c r="H5" s="1">
         <v>27000</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="1">
         <v>3</v>
       </c>
-      <c r="J5" s="2">
+      <c r="J5" s="1">
         <v>40500</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="1">
         <v>4</v>
       </c>
-      <c r="L5" s="2">
+      <c r="L5" s="1">
         <v>60800</v>
       </c>
-      <c r="M5">
+      <c r="M5" s="1">
         <v>5</v>
       </c>
-      <c r="N5" s="2">
+      <c r="N5" s="1">
         <v>91100</v>
       </c>
-      <c r="O5">
+      <c r="O5" s="1">
         <v>5.5</v>
       </c>
-      <c r="P5" s="2">
+      <c r="P5" s="1">
         <v>136700</v>
       </c>
-      <c r="Q5">
+      <c r="Q5" s="1">
         <v>6</v>
       </c>
-      <c r="R5" s="2">
+      <c r="R5" s="1">
         <v>205000</v>
       </c>
-      <c r="S5">
+      <c r="S5" s="1">
         <v>6.5</v>
       </c>
-      <c r="T5" s="2">
+      <c r="T5" s="1">
         <v>307500</v>
       </c>
-      <c r="U5">
+      <c r="U5" s="1">
         <v>7</v>
       </c>
-      <c r="V5" s="2">
+      <c r="V5" s="1">
         <v>461300</v>
       </c>
-      <c r="W5">
+      <c r="W5" s="1">
         <v>7.5</v>
       </c>
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.45">
-      <c r="A6">
+      <c r="A6" s="1">
         <v>5</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="1">
         <v>4</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="1">
         <v>1</v>
       </c>
-      <c r="F6" s="2">
+      <c r="F6" s="1">
         <v>36000</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="1">
         <v>2</v>
       </c>
-      <c r="H6" s="2">
+      <c r="H6" s="1">
         <v>108000</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="1">
         <v>3</v>
       </c>
-      <c r="J6" s="2">
+      <c r="J6" s="1">
         <v>324000</v>
       </c>
-      <c r="K6">
+      <c r="K6" s="1">
         <v>4</v>
       </c>
     </row>

--- a/Assets/Resources/DataBase/Upgrade Data/UpgradeDB.xlsx
+++ b/Assets/Resources/DataBase/Upgrade Data/UpgradeDB.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr defaultThemeVersion="202300"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\LastDance\Assets\Resources\DataBase\Upgrade Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JoYK\Documents\GitHub\Engine GenP 3D\LastDance\Assets\Resources\DataBase\Upgrade Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44F597CF-6B53-435E-89EF-B395194ED9B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="25824" windowHeight="16224"/>
   </bookViews>
   <sheets>
     <sheet name="UpgradeSheet" sheetId="1" r:id="rId1"/>
@@ -19,6 +18,17 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="2"/>
@@ -143,7 +153,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0_);[Red]\(0\)"/>
   </numFmts>
@@ -186,8 +196,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
@@ -526,405 +539,362 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:W6"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="6.83203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="12.58203125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="16" style="1" customWidth="1"/>
-    <col min="4" max="21" width="8.6640625" style="1"/>
-    <col min="22" max="22" width="9.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="8.6640625" style="1"/>
+    <col min="1" max="1" width="6.796875" customWidth="1"/>
+    <col min="2" max="2" width="12.59765625" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="22" max="22" width="9.69921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.45">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.4">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>21</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>28</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>11</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>12</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>5</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>13</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>6</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" t="s">
         <v>14</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" t="s">
         <v>7</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" t="s">
         <v>15</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" t="s">
         <v>8</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" t="s">
         <v>9</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" t="s">
         <v>17</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" t="s">
         <v>10</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" t="s">
         <v>18</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" t="s">
         <v>19</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="W1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.45">
-      <c r="A2" s="1">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.4">
+      <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" t="s">
         <v>29</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" t="s">
         <v>23</v>
       </c>
-      <c r="D2" s="1">
+      <c r="D2">
         <v>8</v>
       </c>
-      <c r="E2" s="1">
+      <c r="E2">
         <v>0</v>
       </c>
-      <c r="F2" s="1">
-        <v>10800</v>
-      </c>
-      <c r="G2" s="1">
+      <c r="F2">
+        <v>100</v>
+      </c>
+      <c r="G2" s="2">
+        <v>15</v>
+      </c>
+      <c r="H2">
+        <v>1000</v>
+      </c>
+      <c r="I2" s="2">
+        <v>30</v>
+      </c>
+      <c r="J2" s="2">
+        <v>5000</v>
+      </c>
+      <c r="K2" s="2">
+        <v>40</v>
+      </c>
+      <c r="L2" s="2">
+        <v>10000</v>
+      </c>
+      <c r="M2" s="2">
+        <v>50</v>
+      </c>
+      <c r="N2" s="2">
+        <v>50000</v>
+      </c>
+      <c r="O2" s="2">
+        <v>60</v>
+      </c>
+      <c r="P2" s="2">
+        <v>100000</v>
+      </c>
+      <c r="Q2" s="2">
+        <v>70</v>
+      </c>
+      <c r="R2" s="2">
+        <v>300000</v>
+      </c>
+      <c r="S2" s="2">
+        <v>75</v>
+      </c>
+      <c r="T2" s="2">
+        <v>500000</v>
+      </c>
+      <c r="U2" s="2">
+        <v>80</v>
+      </c>
+      <c r="V2" s="2">
+        <v>1000000</v>
+      </c>
+      <c r="W2" s="1"/>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.4">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3">
+        <v>8</v>
+      </c>
+      <c r="E3">
+        <v>100</v>
+      </c>
+      <c r="F3">
+        <v>1000</v>
+      </c>
+      <c r="G3">
+        <v>90</v>
+      </c>
+      <c r="H3" s="2">
+        <v>7000</v>
+      </c>
+      <c r="I3">
+        <v>80</v>
+      </c>
+      <c r="J3" s="2">
+        <v>50000</v>
+      </c>
+      <c r="K3">
+        <v>70</v>
+      </c>
+      <c r="L3" s="2">
+        <v>150000</v>
+      </c>
+      <c r="M3">
+        <v>60</v>
+      </c>
+      <c r="N3" s="2">
+        <v>500000</v>
+      </c>
+      <c r="O3">
+        <v>50</v>
+      </c>
+      <c r="P3" s="2">
+        <v>1000000</v>
+      </c>
+      <c r="Q3">
+        <v>40</v>
+      </c>
+      <c r="R3" s="2">
+        <v>2000000</v>
+      </c>
+      <c r="S3">
+        <v>35</v>
+      </c>
+      <c r="T3" s="2">
+        <v>500000</v>
+      </c>
+      <c r="U3">
+        <v>30</v>
+      </c>
+      <c r="V3" s="2">
+        <v>10000000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.4">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4">
+        <v>6</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>500</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+      <c r="H4">
+        <v>5000</v>
+      </c>
+      <c r="I4">
+        <v>3</v>
+      </c>
+      <c r="J4">
+        <v>30000</v>
+      </c>
+      <c r="K4">
+        <v>3.5</v>
+      </c>
+      <c r="L4">
+        <v>100000</v>
+      </c>
+      <c r="M4">
+        <v>4</v>
+      </c>
+      <c r="N4">
+        <v>300000</v>
+      </c>
+      <c r="O4">
+        <v>4.5</v>
+      </c>
+      <c r="P4">
+        <v>500000</v>
+      </c>
+      <c r="Q4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" x14ac:dyDescent="0.4">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" t="s">
         <v>25</v>
       </c>
-      <c r="H2" s="1">
-        <v>15700</v>
-      </c>
-      <c r="I2" s="1">
-        <v>50</v>
-      </c>
-      <c r="J2" s="1">
-        <v>22700</v>
-      </c>
-      <c r="K2" s="1">
-        <v>75</v>
-      </c>
-      <c r="L2" s="1">
-        <v>32900</v>
-      </c>
-      <c r="M2" s="1">
-        <v>100</v>
-      </c>
-      <c r="N2" s="1">
-        <v>47700</v>
-      </c>
-      <c r="O2" s="1">
-        <v>125</v>
-      </c>
-      <c r="P2" s="1">
-        <v>69200</v>
-      </c>
-      <c r="Q2" s="1">
-        <v>150</v>
-      </c>
-      <c r="R2" s="1">
-        <v>100400</v>
-      </c>
-      <c r="S2" s="1">
-        <v>175</v>
-      </c>
-      <c r="T2" s="1">
-        <v>145500</v>
-      </c>
-      <c r="U2" s="1">
-        <v>200</v>
-      </c>
-      <c r="V2" s="1">
-        <v>211000</v>
-      </c>
-      <c r="W2" s="1">
-        <v>225</v>
+      <c r="D5">
+        <v>6</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>500</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+      <c r="H5">
+        <v>5000</v>
+      </c>
+      <c r="I5">
+        <v>3</v>
+      </c>
+      <c r="J5">
+        <v>30000</v>
+      </c>
+      <c r="K5">
+        <v>3.5</v>
+      </c>
+      <c r="L5">
+        <v>100000</v>
+      </c>
+      <c r="M5">
+        <v>4</v>
+      </c>
+      <c r="N5">
+        <v>300000</v>
+      </c>
+      <c r="O5">
+        <v>4.5</v>
+      </c>
+      <c r="P5">
+        <v>500000</v>
+      </c>
+      <c r="Q5">
+        <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.45">
-      <c r="A3" s="1">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.4">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6">
+        <v>4</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>10000</v>
+      </c>
+      <c r="G6">
         <v>2</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D3" s="1">
-        <v>8</v>
-      </c>
-      <c r="E3" s="1">
-        <v>100</v>
-      </c>
-      <c r="F3" s="1">
-        <v>30300</v>
-      </c>
-      <c r="G3" s="1">
-        <v>90</v>
-      </c>
-      <c r="H3" s="1">
-        <v>43900</v>
-      </c>
-      <c r="I3" s="1">
-        <v>80</v>
-      </c>
-      <c r="J3" s="1">
-        <v>63700</v>
-      </c>
-      <c r="K3" s="1">
-        <v>70</v>
-      </c>
-      <c r="L3" s="1">
-        <v>92300</v>
-      </c>
-      <c r="M3" s="1">
-        <v>60</v>
-      </c>
-      <c r="N3" s="1">
-        <v>133800</v>
-      </c>
-      <c r="O3" s="1">
-        <v>50</v>
-      </c>
-      <c r="P3" s="1">
-        <v>194100</v>
-      </c>
-      <c r="Q3" s="1">
-        <v>45</v>
-      </c>
-      <c r="R3" s="1">
-        <v>281400</v>
-      </c>
-      <c r="S3" s="1">
-        <v>40</v>
-      </c>
-      <c r="T3" s="1">
-        <v>408000</v>
-      </c>
-      <c r="U3" s="1">
-        <v>35</v>
-      </c>
-      <c r="V3" s="1">
-        <v>612500</v>
-      </c>
-      <c r="W3" s="1">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.45">
-      <c r="A4" s="1">
+      <c r="H6">
+        <v>100000</v>
+      </c>
+      <c r="I6">
         <v>3</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D4" s="1">
-        <v>6</v>
-      </c>
-      <c r="E4" s="1">
-        <v>1</v>
-      </c>
-      <c r="F4" s="1">
-        <v>21600</v>
-      </c>
-      <c r="G4" s="1">
-        <v>2</v>
-      </c>
-      <c r="H4" s="1">
-        <v>32400</v>
-      </c>
-      <c r="I4" s="1">
-        <v>3</v>
-      </c>
-      <c r="J4" s="1">
-        <v>48600</v>
-      </c>
-      <c r="K4" s="1">
-        <v>4</v>
-      </c>
-      <c r="L4" s="1">
-        <v>72900</v>
-      </c>
-      <c r="M4" s="1">
-        <v>5</v>
-      </c>
-      <c r="N4" s="1">
-        <v>109400</v>
-      </c>
-      <c r="O4" s="1">
-        <v>5.5</v>
-      </c>
-      <c r="P4" s="1">
-        <v>164000</v>
-      </c>
-      <c r="Q4" s="1">
-        <v>6</v>
-      </c>
-      <c r="R4" s="1">
-        <v>246000</v>
-      </c>
-      <c r="S4" s="1">
-        <v>6.5</v>
-      </c>
-      <c r="T4" s="1">
-        <v>369100</v>
-      </c>
-      <c r="U4" s="1">
-        <v>7</v>
-      </c>
-      <c r="V4" s="1">
-        <v>553600</v>
-      </c>
-      <c r="W4" s="1">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.45">
-      <c r="A5" s="1">
-        <v>4</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D5" s="1">
-        <v>6</v>
-      </c>
-      <c r="E5" s="1">
-        <v>1</v>
-      </c>
-      <c r="F5" s="1">
-        <v>18000</v>
-      </c>
-      <c r="G5" s="1">
-        <v>2</v>
-      </c>
-      <c r="H5" s="1">
-        <v>27000</v>
-      </c>
-      <c r="I5" s="1">
-        <v>3</v>
-      </c>
-      <c r="J5" s="1">
-        <v>40500</v>
-      </c>
-      <c r="K5" s="1">
-        <v>4</v>
-      </c>
-      <c r="L5" s="1">
-        <v>60800</v>
-      </c>
-      <c r="M5" s="1">
-        <v>5</v>
-      </c>
-      <c r="N5" s="1">
-        <v>91100</v>
-      </c>
-      <c r="O5" s="1">
-        <v>5.5</v>
-      </c>
-      <c r="P5" s="1">
-        <v>136700</v>
-      </c>
-      <c r="Q5" s="1">
-        <v>6</v>
-      </c>
-      <c r="R5" s="1">
-        <v>205000</v>
-      </c>
-      <c r="S5" s="1">
-        <v>6.5</v>
-      </c>
-      <c r="T5" s="1">
-        <v>307500</v>
-      </c>
-      <c r="U5" s="1">
-        <v>7</v>
-      </c>
-      <c r="V5" s="1">
-        <v>461300</v>
-      </c>
-      <c r="W5" s="1">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.45">
-      <c r="A6" s="1">
-        <v>5</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" s="1">
-        <v>4</v>
-      </c>
-      <c r="E6" s="1">
-        <v>1</v>
-      </c>
-      <c r="F6" s="1">
-        <v>36000</v>
-      </c>
-      <c r="G6" s="1">
-        <v>2</v>
-      </c>
-      <c r="H6" s="1">
-        <v>108000</v>
-      </c>
-      <c r="I6" s="1">
-        <v>3</v>
-      </c>
-      <c r="J6" s="1">
-        <v>324000</v>
-      </c>
-      <c r="K6" s="1">
+      <c r="J6">
+        <v>1000000</v>
+      </c>
+      <c r="K6">
         <v>4</v>
       </c>
     </row>

--- a/Assets/Resources/DataBase/Upgrade Data/UpgradeDB.xlsx
+++ b/Assets/Resources/DataBase/Upgrade Data/UpgradeDB.xlsx
@@ -874,7 +874,7 @@
         <v>22</v>
       </c>
       <c r="D6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E6">
         <v>1</v>
